--- a/data/trans_dic/IP12B$fiebre-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 45,47</t>
+          <t>7,72; 45,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 61,62</t>
+          <t>7,11; 61,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 60,18</t>
+          <t>6,99; 60,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,83</t>
+          <t>0,0; 47,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 43,35</t>
+          <t>13,64; 42,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 43,44</t>
+          <t>7,85; 43,13</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,42</t>
+          <t>0,0; 32,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 27,12</t>
+          <t>3,03; 26,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 23,92</t>
+          <t>2,74; 24,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,19</t>
+          <t>0,0; 24,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,21</t>
+          <t>0,0; 25,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 34,08</t>
+          <t>3,89; 33,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 22,08</t>
+          <t>2,2; 19,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 20,49</t>
+          <t>3,77; 20,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 23,59</t>
+          <t>5,81; 23,79</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,49</t>
+          <t>0,0; 31,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,5</t>
+          <t>0,0; 40,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,28</t>
+          <t>0,0; 40,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 41,94</t>
+          <t>9,09; 42,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 33,03</t>
+          <t>3,92; 29,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 27,73</t>
+          <t>3,2; 28,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 34,82</t>
+          <t>8,42; 38,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 17,73</t>
+          <t>2,26; 18,8</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,58</t>
+          <t>0,0; 28,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 37,47</t>
+          <t>4,7; 43,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 50,65</t>
+          <t>6,66; 56,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,93</t>
+          <t>0,0; 22,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 55,55</t>
+          <t>6,11; 56,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 32,15</t>
+          <t>3,97; 32,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 15,66</t>
+          <t>1,96; 18,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 38,65</t>
+          <t>10,46; 38,48</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,36</t>
+          <t>1,51; 13,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 21,85</t>
+          <t>6,89; 21,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,74; 22,62</t>
+          <t>7,51; 23,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 20,06</t>
+          <t>5,35; 19,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 27,04</t>
+          <t>8,93; 25,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,29; 26,81</t>
+          <t>9,32; 26,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,62</t>
+          <t>4,37; 14,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 20,15</t>
+          <t>9,51; 20,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,97; 20,8</t>
+          <t>9,25; 20,59</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4025</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2820</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3473</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1324; 7845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>631; 5495</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>714; 6153</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3359</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3731; 11700</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1255; 6898</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2166</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2506</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4633</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3948</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>581; 5175</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>555; 5012</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3966</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3544</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>605; 5213</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>622; 5618</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1255; 6713</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2081; 8525</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4078</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5383</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4028</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3814</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3349</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1647; 7661</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>625; 4716</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>672; 5938</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2317; 10485</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>624; 5178</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2583</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2269</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5244</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4431</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>676; 6303</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699; 5885</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4673</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>565; 5228</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>689; 5561</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>719; 6784</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2471; 9091</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2564</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7756</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7798</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>18034</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>15325</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>663; 5848</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4221; 13253</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4141; 12848</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2498; 9219</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5674; 16080</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4462; 12443</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3959; 12714</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>11872; 25853</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>9521; 21208</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$fiebre-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 45,76</t>
+          <t>8,85; 45,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 61,93</t>
+          <t>7,37; 62,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 60,26</t>
+          <t>12,65; 60,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,19</t>
+          <t>0,0; 46,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,64; 42,77</t>
+          <t>13,6; 42,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 43,13</t>
+          <t>7,36; 43,8</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,65</t>
+          <t>0,0; 30,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 26,98</t>
+          <t>3,05; 27,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 24,72</t>
+          <t>2,83; 24,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,56</t>
+          <t>0,0; 24,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,09</t>
+          <t>0,0; 28,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 33,51</t>
+          <t>3,82; 32,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 19,89</t>
+          <t>2,23; 19,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 20,15</t>
+          <t>3,85; 21,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 23,79</t>
+          <t>6,24; 23,01</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,73</t>
+          <t>0,0; 39,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,51</t>
+          <t>0,0; 41,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,32 +913,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,46</t>
+          <t>0,0; 47,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 42,28</t>
+          <t>8,51; 41,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 29,58</t>
+          <t>3,88; 32,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 28,31</t>
+          <t>3,22; 28,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 38,08</t>
+          <t>9,62; 37,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 18,8</t>
+          <t>2,25; 18,01</t>
         </is>
       </c>
     </row>
@@ -1013,42 +1013,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,49</t>
+          <t>0,0; 19,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 43,81</t>
+          <t>4,56; 40,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 56,07</t>
+          <t>6,52; 56,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,14</t>
+          <t>0,0; 22,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 56,58</t>
+          <t>6,5; 54,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 32,07</t>
+          <t>3,94; 33,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 18,51</t>
+          <t>1,91; 17,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 38,48</t>
+          <t>10,91; 39,71</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,33</t>
+          <t>1,51; 14,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,89; 21,62</t>
+          <t>6,78; 20,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 23,31</t>
+          <t>7,36; 22,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 19,74</t>
+          <t>5,49; 20,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,93; 25,3</t>
+          <t>8,06; 24,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 26,0</t>
+          <t>9,11; 26,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 14,04</t>
+          <t>4,96; 14,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,51; 20,71</t>
+          <t>9,88; 20,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,25; 20,59</t>
+          <t>10,26; 20,5</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1324; 7845</t>
+          <t>1517; 7714</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>631; 5495</t>
+          <t>654; 5531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>714; 6153</t>
+          <t>1292; 6135</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3359</t>
+          <t>0; 3331</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3731; 11700</t>
+          <t>3720; 11520</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1255; 6898</t>
+          <t>1177; 7003</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3948</t>
+          <t>0; 3721</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>581; 5175</t>
+          <t>585; 5300</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>555; 5012</t>
+          <t>573; 5014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3966</t>
+          <t>0; 3963</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3544</t>
+          <t>0; 4053</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>605; 5213</t>
+          <t>595; 5067</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>622; 5618</t>
+          <t>629; 5597</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1255; 6713</t>
+          <t>1281; 7240</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2081; 8525</t>
+          <t>2235; 8243</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4028</t>
+          <t>0; 5046</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3814</t>
+          <t>0; 3902</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1758,32 +1758,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3349</t>
+          <t>0; 3931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1647; 7661</t>
+          <t>1542; 7595</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>625; 4716</t>
+          <t>618; 5113</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>672; 5938</t>
+          <t>676; 6051</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2317; 10485</t>
+          <t>2648; 10292</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>624; 5178</t>
+          <t>620; 4959</t>
         </is>
       </c>
     </row>
@@ -1911,42 +1911,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4431</t>
+          <t>0; 3067</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>676; 6303</t>
+          <t>656; 5892</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>699; 5885</t>
+          <t>685; 5973</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4673</t>
+          <t>0; 4800</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>565; 5228</t>
+          <t>601; 5080</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>689; 5561</t>
+          <t>684; 5859</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>719; 6784</t>
+          <t>700; 6267</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2471; 9091</t>
+          <t>2578; 9382</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>663; 5848</t>
+          <t>661; 6276</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4221; 13253</t>
+          <t>4156; 12806</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4141; 12848</t>
+          <t>4059; 12160</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2498; 9219</t>
+          <t>2566; 9752</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5674; 16080</t>
+          <t>5124; 15427</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4462; 12443</t>
+          <t>4358; 12783</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3959; 12714</t>
+          <t>4495; 12777</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11872; 25853</t>
+          <t>12336; 26100</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9521; 21208</t>
+          <t>10561; 21110</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$fiebre-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,27 +630,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>30,65%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,16%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>23,48%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>31,79%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,65%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,85; 45,0</t>
+          <t>6,87; 60,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 62,34</t>
+          <t>0,0; 40,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,65; 60,08</t>
+          <t>8,18; 45,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,79</t>
+          <t>8,86; 61,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 42,11</t>
+          <t>14,37; 43,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 43,8</t>
+          <t>7,74; 43,44</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,16%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>10,09%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>10,07%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,68%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,77</t>
+          <t>0,0; 25,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 27,63</t>
+          <t>0,0; 29,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 24,73</t>
+          <t>3,91; 34,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,54</t>
+          <t>0,0; 29,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,69</t>
+          <t>3,06; 27,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 32,57</t>
+          <t>2,65; 23,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 19,82</t>
+          <t>2,4; 22,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 21,74</t>
+          <t>3,65; 20,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 23,01</t>
+          <t>6,11; 23,59</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15,53%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22,51%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,39%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>10,59%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,87%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,75</t>
+          <t>0,0; 47,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,44</t>
+          <t>8,74; 41,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>3,89; 33,03</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 31,49</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 39,5</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 47,48</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>8,51; 41,92</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3,88; 32,07</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 28,85</t>
+          <t>3,28; 27,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 37,38</t>
+          <t>8,7; 34,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 18,01</t>
+          <t>2,25; 17,73</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25,36%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>17,95%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6,47; 50,65</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 22,93</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6,17; 55,55</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 19,72</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4,56; 40,95</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6,52; 56,91</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,74</t>
+          <t>0,0; 28,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 54,98</t>
+          <t>4,56; 37,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 33,79</t>
+          <t>4,03; 32,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 17,1</t>
+          <t>1,89; 15,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 39,71</t>
+          <t>10,08; 38,65</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,84%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>13,07%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>13,73%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 14,3</t>
+          <t>5,35; 20,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 20,89</t>
+          <t>9,62; 27,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 22,06</t>
+          <t>9,29; 26,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 20,88</t>
+          <t>1,44; 13,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 24,27</t>
+          <t>7,14; 21,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 26,71</t>
+          <t>7,74; 22,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 14,11</t>
+          <t>4,38; 13,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,88; 20,91</t>
+          <t>9,37; 20,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,26; 20,5</t>
+          <t>9,97; 20,8</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,27 +1316,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1369,27 +1369,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4025</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2820</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1517; 7714</t>
+          <t>701; 6145</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>654; 5531</t>
+          <t>0; 2906</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1292; 6135</t>
+          <t>1402; 7794</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3331</t>
+          <t>786; 5467</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3720; 11520</t>
+          <t>3931; 11857</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1177; 7003</t>
+          <t>1238; 6946</t>
         </is>
       </c>
     </row>
@@ -1479,22 +1479,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1220</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1933</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2166</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1286</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2467</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3721</t>
+          <t>0; 4067</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>585; 5300</t>
+          <t>0; 4127</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>573; 5014</t>
+          <t>608; 5302</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3963</t>
+          <t>0; 3558</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4053</t>
+          <t>586; 5202</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>595; 5067</t>
+          <t>537; 4849</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>629; 5597</t>
+          <t>678; 6235</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1281; 7240</t>
+          <t>1214; 6825</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235; 8243</t>
+          <t>2188; 8453</t>
         </is>
       </c>
     </row>
@@ -1642,27 +1642,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4078</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1344</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1286</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4078</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5046</t>
+          <t>0; 3914</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3902</t>
+          <t>1583; 7598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>620; 5266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3998</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3719</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3931</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1542; 7595</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>618; 5113</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>676; 6051</t>
+          <t>689; 5817</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2648; 10292</t>
+          <t>2395; 9586</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>620; 4959</t>
+          <t>619; 4881</t>
         </is>
       </c>
     </row>
@@ -1800,27 +1800,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>746</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2583</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2661</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2661</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>679; 5315</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4839</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>570; 5132</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3067</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>656; 5892</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>685; 5973</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4800</t>
+          <t>0; 4444</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>601; 5080</t>
+          <t>656; 5390</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>684; 5859</t>
+          <t>700; 5574</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>700; 6267</t>
+          <t>692; 5739</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2578; 9382</t>
+          <t>2382; 9132</t>
         </is>
       </c>
     </row>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7756</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2564</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>8010</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>7570</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5233</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>10024</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7756</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>661; 6276</t>
+          <t>2501; 9368</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4156; 12806</t>
+          <t>6114; 17188</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4059; 12160</t>
+          <t>4446; 12831</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2566; 9752</t>
+          <t>632; 5862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5124; 15427</t>
+          <t>4374; 13392</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4358; 12783</t>
+          <t>4268; 12467</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4495; 12777</t>
+          <t>3964; 12340</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12336; 26100</t>
+          <t>11696; 25154</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10561; 21110</t>
+          <t>10270; 21420</t>
         </is>
       </c>
     </row>
